--- a/tame_output/ON/bt/strategyON_20240802.xlsx
+++ b/tame_output/ON/bt/strategyON_20240802.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,17 +982,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>453.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.5%</t>
+          <t>-682.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-200.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-230.6%</t>
+          <t>-228.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-64.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2042"/>
+  <dimension ref="A1:G2043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.776807407941017</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48527,6 +48527,29 @@
       </c>
       <c r="G2042" t="n">
         <v>3.763156132287544</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="2" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B2043" t="n">
+        <v>3.783240727848819</v>
+      </c>
+      <c r="C2043" t="n">
+        <v>3.837559870562694</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>-5.204266160892076</v>
+      </c>
+      <c r="E2043" t="n">
+        <v>1.755496981892116</v>
+      </c>
+      <c r="F2043" t="n">
+        <v>-0.04053481827050259</v>
+      </c>
+      <c r="G2043" t="n">
+        <v>3.813238979600393</v>
       </c>
     </row>
   </sheetData>
